--- a/output/pdf_financials_xlsx/RTM.xlsx
+++ b/output/pdf_financials_xlsx/RTM.xlsx
@@ -5870,19 +5870,19 @@
         <v>1.711001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.161987</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.161987</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.176047</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.176047</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.176047</v>
       </c>
     </row>
     <row r="93">
@@ -9797,7 +9797,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10785,7 +10789,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RTM.xlsx
+++ b/output/pdf_financials_xlsx/RTM.xlsx
@@ -922,46 +922,46 @@
         <v>0.250711</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.12455</v>
+        <v>5.474988</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.147446</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>3.248356</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.970387</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.113921</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.5927519999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.617917</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>1.088566</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.305814</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.773097</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.154781</v>
+        <v>0.282883</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.175254</v>
+        <v>0.359287</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.451214</v>
+        <v>0.686313</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.301178</v>
+        <v>0.47967</v>
       </c>
     </row>
     <row r="11">
@@ -983,43 +983,43 @@
         <v>-0.909673</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-1.147446</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-3.248356</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.970387</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-0.113921</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0.5927519999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-0.617917</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-1.088566</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-0.305814</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-0.773097</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.154781</v>
+        <v>-0.282883</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.175254</v>
+        <v>-0.359287</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.451214</v>
+        <v>-0.686313</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.301178</v>
+        <v>-0.47967</v>
       </c>
     </row>
     <row r="12">
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000907</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000143</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003884</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.021569</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000421</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.323126</v>
+        <v>-0.324033</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7828079999999999</v>
+        <v>-0.782951</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.132088</v>
+        <v>-2.135972</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.738249</v>
+        <v>-4.759818</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.990821</v>
@@ -2005,7 +2005,7 @@
         <v>-0.305515</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.310721</v>
+        <v>-2.311142</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-1.502275</v>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.323126</v>
+        <v>-0.324033</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7828079999999999</v>
+        <v>-0.782951</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.132088</v>
+        <v>-2.135972</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.73691</v>
+        <v>-4.758479</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.988525</v>
@@ -2121,7 +2121,7 @@
         <v>-0.305515</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.310721</v>
+        <v>-2.311142</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-1.502275</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005176</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.031089</v>
@@ -2410,37 +2410,37 @@
         <v>0.001204</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001391</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07815999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001526</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.045582</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.049104</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005181</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.399789</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00123</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.093599</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.26598</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001146</v>
       </c>
     </row>
     <row r="35">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005176</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.031089</v>
@@ -2526,37 +2526,37 @@
         <v>0.001204</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001391</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07815999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.255</v>
+        <v>0.256526</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.000125</v>
+        <v>0.045707</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.086023</v>
+        <v>0.135127</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005181</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.399789</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.153</v>
+        <v>0.15423</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.093599</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.26598</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001146</v>
       </c>
     </row>
     <row r="37">
@@ -3222,37 +3222,37 @@
         <v>0.006636</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.004795</v>
+        <v>0.003404</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.078667</v>
+        <v>0.000507</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.017997</v>
+        <v>0.016471</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.046015</v>
+        <v>0.000433</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.049737</v>
+        <v>0.000633</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.010199</v>
+        <v>0.005018</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.406309</v>
+        <v>0.00652</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.002952</v>
+        <v>0.001722</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.098965</v>
+        <v>0.005366</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.297461</v>
+        <v>0.031481</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.0028</v>
+        <v>0.001654</v>
       </c>
     </row>
     <row r="49">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -33201,7 +33201,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -33220,46 +33220,46 @@
         </is>
       </c>
       <c r="H252" s="5" t="n">
-        <v>-5.474988</v>
+        <v>5.474988</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>-1.147446</v>
+        <v>1.147446</v>
       </c>
       <c r="J252" s="5" t="n">
-        <v>-3.248356</v>
+        <v>3.248356</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>-0.970387</v>
+        <v>0.970387</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>-0.113921</v>
+        <v>0.113921</v>
       </c>
       <c r="M252" s="5" t="n">
-        <v>-0.5927519999999999</v>
+        <v>0.5927519999999999</v>
       </c>
       <c r="N252" s="5" t="n">
-        <v>-0.617917</v>
+        <v>0.617917</v>
       </c>
       <c r="O252" s="5" t="n">
-        <v>-1.088566</v>
+        <v>1.088566</v>
       </c>
       <c r="P252" s="5" t="n">
-        <v>-0.305814</v>
+        <v>0.305814</v>
       </c>
       <c r="Q252" s="5" t="n">
-        <v>-0.773097</v>
+        <v>0.773097</v>
       </c>
       <c r="R252" s="5" t="n">
-        <v>-0.282883</v>
+        <v>0.282883</v>
       </c>
       <c r="S252" s="5" t="n">
-        <v>-0.359287</v>
+        <v>0.359287</v>
       </c>
       <c r="T252" s="5" t="n">
-        <v>-0.686313</v>
+        <v>0.686313</v>
       </c>
       <c r="U252" s="5" t="n">
-        <v>-0.47967</v>
+        <v>0.47967</v>
       </c>
     </row>
     <row r="253">
@@ -35072,7 +35072,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -36084,7 +36084,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -44844,7 +44844,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" s="5" t="n">

--- a/output/pdf_financials_xlsx/RTM.xlsx
+++ b/output/pdf_financials_xlsx/RTM.xlsx
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.008713</v>
+        <v>0.016323</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.01399</v>
+        <v>0.081039</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.238252</v>
+        <v>0.302703</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.114543</v>
+        <v>0.233543</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.012625</v>
+        <v>0.020235</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.021545</v>
+        <v>0.08859400000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.250711</v>
+        <v>0.315162</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>5.474988</v>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.016458</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.042218</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0.339617</v>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.465061</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>1.256423</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>4.718777</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0352</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.119201</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.692403</v>
@@ -16427,7 +16427,11 @@
           <t>Short term investments – Notes 3 and 5</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -16625,7 +16629,11 @@
           <t>Prepaid expenses – Note 8</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -16819,7 +16827,11 @@
           <t>Equipment – Note 4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -17118,7 +17130,11 @@
           <t>Due to related parties – Notes 6 and 8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -17316,7 +17332,11 @@
           <t>Share capital – Notes 5 and 7</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -17415,7 +17435,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -17712,7 +17736,11 @@
           <t>Short term investments – Notes 3 and 4</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -17813,7 +17841,11 @@
           <t>Prepaid expenses – Note 7</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -18011,7 +18043,11 @@
           <t>Due to related parties – Notes 5 and 7</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -18211,7 +18247,11 @@
           <t>Share capital – Notes 4 and 6</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -18310,7 +18350,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -18512,7 +18556,11 @@
           <t>Prepaid expenses – Note 6</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>0.002197</v>
       </c>
@@ -18710,7 +18758,11 @@
           <t>Due to related parties – Note 4</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="n">
         <v>0.016458</v>
       </c>
@@ -18809,7 +18861,11 @@
           <t>Share capital – Notes 3 and 5</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>0.465061</v>
       </c>
@@ -18908,7 +18964,11 @@
           <t>Contributed surplus – Note 5</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>0.0352</v>
       </c>
@@ -40856,7 +40916,11 @@
           <t>Administrative and consulting fees – Note 8</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -43345,7 +43409,11 @@
           <t>Administrative and consulting fees – Note 7</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -43444,7 +43512,11 @@
           <t>Loan interest expense – Note 7</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -44446,7 +44518,11 @@
           <t>Administrative and consulting fees – Note 6</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E365" s="5" t="n">
         <v>0.00761</v>
       </c>
@@ -44545,7 +44621,11 @@
           <t>Loan interest expense – Note 6</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E366" s="5" t="n">
         <v>0.000303</v>
       </c>

--- a/output/pdf_financials_xlsx/RTM.xlsx
+++ b/output/pdf_financials_xlsx/RTM.xlsx
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.016323</v>
+        <v>0.042099</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.081039</v>
+        <v>0.118625</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.302703</v>
+        <v>0.358099</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.233543</v>
+        <v>0.308478</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.020235</v>
+        <v>0.046011</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.08859400000000001</v>
+        <v>0.12618</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.315162</v>
+        <v>0.370558</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>5.474988</v>
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011481</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002139</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -7163,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.054577</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011481</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002139</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
         <v>-0.609375</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.65029</v>
+        <v>-0.661771</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.629336</v>
@@ -8361,7 +8361,7 @@
         <v>-0.004496</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.44051</v>
+        <v>-0.442649</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-0.646018</v>
@@ -20345,7 +20345,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -21293,7 +21297,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -21394,7 +21402,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -22586,7 +22598,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -26758,7 +26774,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -27473,7 +27493,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27782,7 +27806,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -29976,7 +30004,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30384,7 +30416,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E223" s="5" t="n">
         <v>0.45</v>
       </c>
@@ -41516,7 +41552,11 @@
           <t>Office Expenses – Note 8</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -43716,7 +43756,11 @@
           <t>Office Expenses</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E357" s="5" t="n">
         <v>0.025776</v>
       </c>
